--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T15:08:49+00:00</t>
+    <t>2026-07-01T07:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T07:03:00+00:00</t>
+    <t>2026-07-01T08:10:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:10:51+00:00</t>
+    <t>2026-07-01T14:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:14:35+00:00</t>
+    <t>2026-07-02T07:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T07:31:32+00:00</t>
+    <t>2026-07-02T18:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T18:50:30+00:00</t>
+    <t>2026-07-03T07:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:01:21+00:00</t>
+    <t>2026-07-03T07:53:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:53:06+00:00</t>
+    <t>2026-07-04T06:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T06:47:13+00:00</t>
+    <t>2026-07-06T08:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T08:19:21+00:00</t>
+    <t>2026-07-06T11:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:30:59+00:00</t>
+    <t>2026-07-07T07:34:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T07:34:33+00:00</t>
+    <t>2026-07-07T09:30:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T09:30:03+00:00</t>
+    <t>2026-07-07T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T16:17:51+00:00</t>
+    <t>2026-07-07T18:51:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T18:51:54+00:00</t>
+    <t>2026-07-08T06:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T06:29:02+00:00</t>
+    <t>2026-07-08T13:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T13:11:45+00:00</t>
+    <t>2026-07-09T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T07:37:59+00:00</t>
+    <t>2026-07-10T07:33:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T07:33:56+00:00</t>
+    <t>2026-07-11T06:13:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T06:13:55+00:00</t>
+    <t>2026-07-12T06:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-12T06:33:38+00:00</t>
+    <t>2026-07-13T06:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T06:51:55+00:00</t>
+    <t>2026-07-14T06:10:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T06:10:10+00:00</t>
+    <t>2026-07-15T06:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:13:44+00:00</t>
+    <t>2026-07-16T06:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T06:16:18+00:00</t>
+    <t>2026-07-17T06:14:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:14:46+00:00</t>
+    <t>2026-07-18T06:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-18T06:04:03+00:00</t>
+    <t>2026-07-19T06:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T06:29:36+00:00</t>
+    <t>2026-07-20T06:45:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T06:45:38+00:00</t>
+    <t>2026-07-21T06:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T06:27:40+00:00</t>
+    <t>2026-07-22T06:27:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T06:27:15+00:00</t>
+    <t>2026-07-23T06:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T06:30:53+00:00</t>
+    <t>2026-07-24T06:26:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T06:26:28+00:00</t>
+    <t>2026-07-25T06:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T06:16:33+00:00</t>
+    <t>2026-07-26T06:35:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T06:35:59+00:00</t>
+    <t>2026-07-27T07:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:02:45+00:00</t>
+    <t>2026-07-28T12:20:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T12:20:45+00:00</t>
+    <t>2026-07-29T06:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:29:58+00:00</t>
+    <t>2026-07-29T12:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:32:03+00:00</t>
+    <t>2026-07-30T06:27:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:27:34+00:00</t>
+    <t>2026-07-31T06:43:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T06:43:14+00:00</t>
+    <t>2026-08-01T06:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-01T06:27:03+00:00</t>
+    <t>2026-08-03T06:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T06:59:50+00:00</t>
+    <t>2026-08-04T06:27:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T06:27:06+00:00</t>
+    <t>2026-08-05T06:27:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T06:27:16+00:00</t>
+    <t>2026-08-07T05:33:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T05:33:47+00:00</t>
+    <t>2026-08-08T04:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-08T04:55:01+00:00</t>
+    <t>2026-08-10T05:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T05:24:31+00:00</t>
+    <t>2026-08-11T05:05:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T05:05:23+00:00</t>
+    <t>2026-08-13T05:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T05:34:44+00:00</t>
+    <t>2026-08-14T05:32:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:32:34+00:00</t>
+    <t>2026-08-15T04:27:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T04:27:21+00:00</t>
+    <t>2026-08-16T04:34:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T04:34:25+00:00</t>
+    <t>2026-08-17T04:38:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T04:38:40+00:00</t>
+    <t>2026-08-18T04:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T04:33:50+00:00</t>
+    <t>2026-08-19T04:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T04:34:44+00:00</t>
+    <t>2026-08-22T04:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:30:53+00:00</t>
+    <t>2026-08-23T04:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T04:36:38+00:00</t>
+    <t>2026-08-24T04:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T04:43:24+00:00</t>
+    <t>2026-08-25T04:38:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T04:38:28+00:00</t>
+    <t>2026-08-26T04:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T04:39:12+00:00</t>
+    <t>2026-08-27T13:42:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T13:42:18+00:00</t>
+    <t>2026-08-28T16:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T16:02:20+00:00</t>
+    <t>2026-08-29T10:44:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-29T10:44:20+00:00</t>
+    <t>2026-08-30T09:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T09:42:59+00:00</t>
+    <t>2026-08-31T10:24:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:24:56+00:00</t>
+    <t>2026-09-01T09:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:09:22+00:00</t>
+    <t>2026-09-03T08:31:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:31:21+00:00</t>
+    <t>2026-09-04T08:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:27:47+00:00</t>
+    <t>2026-09-05T08:04:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T08:04:10+00:00</t>
+    <t>2026-09-06T08:20:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T08:20:40+00:00</t>
+    <t>2026-09-07T08:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:53:36+00:00</t>
+    <t>2026-09-08T08:34:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:34:00+00:00</t>
+    <t>2026-09-09T08:36:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:36:15+00:00</t>
+    <t>2026-09-10T08:37:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:37:57+00:00</t>
+    <t>2026-09-11T08:32:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:32:41+00:00</t>
+    <t>2026-09-12T08:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-vs-sms-all.xlsx
+++ b/ig/main/ValueSet-vs-sms-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T08:21:35+00:00</t>
+    <t>2026-09-13T08:45:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
